--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/142.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/142.xlsx
@@ -426,13 +426,13 @@
         <v>-6.580526566397184</v>
       </c>
       <c r="E2">
-        <v>-10.70505650782189</v>
+        <v>-14.76341151485996</v>
       </c>
       <c r="F2">
-        <v>-2.072052689220704</v>
+        <v>-2.943713885960123</v>
       </c>
       <c r="G2">
-        <v>-4.558960033889764</v>
+        <v>-7.757006614645437</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.505068455036332</v>
       </c>
       <c r="E3">
-        <v>-11.44978670075332</v>
+        <v>-14.09736808628581</v>
       </c>
       <c r="F3">
-        <v>-2.287156509440457</v>
+        <v>-2.783280657590332</v>
       </c>
       <c r="G3">
-        <v>-3.28697560569991</v>
+        <v>-7.722192917754461</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.528967790863593</v>
       </c>
       <c r="E4">
-        <v>-9.714597729812244</v>
+        <v>-14.10213656941588</v>
       </c>
       <c r="F4">
-        <v>-3.069925600185461</v>
+        <v>-2.804083448176836</v>
       </c>
       <c r="G4">
-        <v>-4.18600390507209</v>
+        <v>-7.098956235622347</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.532276625288292</v>
       </c>
       <c r="E5">
-        <v>-13.86820918760166</v>
+        <v>-15.55767868496129</v>
       </c>
       <c r="F5">
-        <v>-2.70723155980892</v>
+        <v>-2.934620896979593</v>
       </c>
       <c r="G5">
-        <v>-4.279255351822281</v>
+        <v>-7.267850337399345</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.49123467937664</v>
       </c>
       <c r="E6">
-        <v>-12.349345420007</v>
+        <v>-16.04862413755486</v>
       </c>
       <c r="F6">
-        <v>-2.588955605302401</v>
+        <v>-2.616513732058735</v>
       </c>
       <c r="G6">
-        <v>-4.35638775234176</v>
+        <v>-7.131121496081906</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.34361219265132</v>
       </c>
       <c r="E7">
-        <v>-13.80627324859875</v>
+        <v>-16.544039193994</v>
       </c>
       <c r="F7">
-        <v>-2.793325440716679</v>
+        <v>-2.703313381993679</v>
       </c>
       <c r="G7">
-        <v>-2.972122861641985</v>
+        <v>-7.909573105822751</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.04779619752614</v>
       </c>
       <c r="E8">
-        <v>-14.24603788795763</v>
+        <v>-17.17304423365941</v>
       </c>
       <c r="F8">
-        <v>-2.652943673699052</v>
+        <v>-2.829248421506482</v>
       </c>
       <c r="G8">
-        <v>-2.956990357981976</v>
+        <v>-7.514313831707006</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.55462423409534</v>
       </c>
       <c r="E9">
-        <v>-15.86224573282117</v>
+        <v>-18.12904132447068</v>
       </c>
       <c r="F9">
-        <v>-2.404529543477925</v>
+        <v>-2.612779451806915</v>
       </c>
       <c r="G9">
-        <v>-2.877722655589667</v>
+        <v>-7.31843216269387</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.83376331484727</v>
       </c>
       <c r="E10">
-        <v>-15.6323668067698</v>
+        <v>-18.38328796915733</v>
       </c>
       <c r="F10">
-        <v>-2.126903036797073</v>
+        <v>-2.425524515301879</v>
       </c>
       <c r="G10">
-        <v>-2.424843336362907</v>
+        <v>-7.445828576136103</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.85530914187939</v>
       </c>
       <c r="E11">
-        <v>-18.77825694363233</v>
+        <v>-19.41834315919451</v>
       </c>
       <c r="F11">
-        <v>-2.156020979372879</v>
+        <v>-2.524867304450012</v>
       </c>
       <c r="G11">
-        <v>-2.252708210502963</v>
+        <v>-6.903206988430781</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.60914024484609</v>
       </c>
       <c r="E12">
-        <v>-17.1835457648832</v>
+        <v>-20.80671894825815</v>
       </c>
       <c r="F12">
-        <v>-2.093936499267862</v>
+        <v>-2.382634136287129</v>
       </c>
       <c r="G12">
-        <v>-2.299330623332519</v>
+        <v>-6.485909412660108</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.0926279920448</v>
       </c>
       <c r="E13">
-        <v>-17.75732606402507</v>
+        <v>-21.34235138235941</v>
       </c>
       <c r="F13">
-        <v>-2.11466970699253</v>
+        <v>-2.231204433218365</v>
       </c>
       <c r="G13">
-        <v>-2.272213944820349</v>
+        <v>-5.135253180275014</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.32835557059576</v>
       </c>
       <c r="E14">
-        <v>-18.74802937963113</v>
+        <v>-22.06214326893059</v>
       </c>
       <c r="F14">
-        <v>-1.40754795583858</v>
+        <v>-2.000647419099387</v>
       </c>
       <c r="G14">
-        <v>-0.8111443976094816</v>
+        <v>-5.250791219595579</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.34809831245729</v>
       </c>
       <c r="E15">
-        <v>-21.77201299620717</v>
+        <v>-23.44854011485288</v>
       </c>
       <c r="F15">
-        <v>-1.401148817651954</v>
+        <v>-1.860731194562134</v>
       </c>
       <c r="G15">
-        <v>-1.894431040606417</v>
+        <v>-4.377085283053284</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.19271807848804</v>
       </c>
       <c r="E16">
-        <v>-23.01946720262611</v>
+        <v>-23.73175087929259</v>
       </c>
       <c r="F16">
-        <v>-1.831459175649407</v>
+        <v>-1.754469052498416</v>
       </c>
       <c r="G16">
-        <v>0.07236406427459496</v>
+        <v>-4.390588998307971</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.915139669398837</v>
       </c>
       <c r="E17">
-        <v>-22.09739743908031</v>
+        <v>-24.71811138832529</v>
       </c>
       <c r="F17">
-        <v>-1.036843602676968</v>
+        <v>-1.385321201686664</v>
       </c>
       <c r="G17">
-        <v>-0.7926483796815735</v>
+        <v>-3.974609019661929</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.576807528407529</v>
       </c>
       <c r="E18">
-        <v>-22.61364800442874</v>
+        <v>-25.55384126644086</v>
       </c>
       <c r="F18">
-        <v>-1.179240787585605</v>
+        <v>-1.639482544948414</v>
       </c>
       <c r="G18">
-        <v>1.425456858176593</v>
+        <v>-3.390966462179497</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.231076613163864</v>
       </c>
       <c r="E19">
-        <v>-24.6345746283058</v>
+        <v>-25.92374966575741</v>
       </c>
       <c r="F19">
-        <v>-1.519712215647244</v>
+        <v>-1.31093132381306</v>
       </c>
       <c r="G19">
-        <v>0.3465268931093383</v>
+        <v>-2.963621380697136</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.921252899937366</v>
       </c>
       <c r="E20">
-        <v>-25.39306232527252</v>
+        <v>-27.45023032663297</v>
       </c>
       <c r="F20">
-        <v>-0.5738839718655745</v>
+        <v>-1.225592913976655</v>
       </c>
       <c r="G20">
-        <v>1.298404741470443</v>
+        <v>-2.681453652748435</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.69741693042316</v>
       </c>
       <c r="E21">
-        <v>-26.16643964477648</v>
+        <v>-27.24883550208985</v>
       </c>
       <c r="F21">
-        <v>-1.035808971790871</v>
+        <v>-0.7643347498106116</v>
       </c>
       <c r="G21">
-        <v>0.9421834203537852</v>
+        <v>-2.978055359248359</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.595403959677968</v>
       </c>
       <c r="E22">
-        <v>-23.27578335993427</v>
+        <v>-29.14689104071678</v>
       </c>
       <c r="F22">
-        <v>-0.347712334777017</v>
+        <v>-0.3839401547710506</v>
       </c>
       <c r="G22">
-        <v>2.436669614238056</v>
+        <v>-2.526980287340502</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.6368462902638871</v>
       </c>
       <c r="E23">
-        <v>-26.33021643573788</v>
+        <v>-29.20815676556656</v>
       </c>
       <c r="F23">
-        <v>-0.8880804142778157</v>
+        <v>-0.3201086478135291</v>
       </c>
       <c r="G23">
-        <v>2.26753715318223</v>
+        <v>-2.420883923897939</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.1638275753306947</v>
       </c>
       <c r="E24">
-        <v>-27.55009223545012</v>
+        <v>-30.23818082098122</v>
       </c>
       <c r="F24">
-        <v>-0.3388073851969223</v>
+        <v>-0.4805178535286393</v>
       </c>
       <c r="G24">
-        <v>2.865117107384993</v>
+        <v>-2.054313837425519</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.7894415488279841</v>
       </c>
       <c r="E25">
-        <v>-28.70549615071515</v>
+        <v>-29.67413447671883</v>
       </c>
       <c r="F25">
-        <v>0.2738962210185376</v>
+        <v>-0.2534068478053073</v>
       </c>
       <c r="G25">
-        <v>1.425205256715608</v>
+        <v>-2.12163047042106</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.238451142345404</v>
       </c>
       <c r="E26">
-        <v>-27.37477236424316</v>
+        <v>-29.46029766983963</v>
       </c>
       <c r="F26">
-        <v>0.9127025124636128</v>
+        <v>-0.4496959592052754</v>
       </c>
       <c r="G26">
-        <v>2.125047962626459</v>
+        <v>-1.852334143529045</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.516579394599951</v>
       </c>
       <c r="E27">
-        <v>-30.41312256460854</v>
+        <v>-30.86513672615816</v>
       </c>
       <c r="F27">
-        <v>0.7146564338023069</v>
+        <v>-0.3544411631899574</v>
       </c>
       <c r="G27">
-        <v>1.922866325452089</v>
+        <v>-2.362154846031268</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.628177800439428</v>
       </c>
       <c r="E28">
-        <v>-29.34240790599795</v>
+        <v>-30.60247844100227</v>
       </c>
       <c r="F28">
-        <v>0.5845986097257706</v>
+        <v>-0.2273878276833748</v>
       </c>
       <c r="G28">
-        <v>2.358818825336555</v>
+        <v>-2.200822030265966</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.587123902294555</v>
       </c>
       <c r="E29">
-        <v>-30.39488413554264</v>
+        <v>-30.65838018838995</v>
       </c>
       <c r="F29">
-        <v>0.1859791034572177</v>
+        <v>-0.2830126987813616</v>
       </c>
       <c r="G29">
-        <v>2.209135819323947</v>
+        <v>-2.747634768624005</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.412127718469946</v>
       </c>
       <c r="E30">
-        <v>-28.65216884080082</v>
+        <v>-30.73521933535211</v>
       </c>
       <c r="F30">
-        <v>0.6687135209082408</v>
+        <v>-0.1036098568874615</v>
       </c>
       <c r="G30">
-        <v>1.142928280764111</v>
+        <v>-1.93611743003692</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.125450119862307</v>
       </c>
       <c r="E31">
-        <v>-28.85421123712704</v>
+        <v>-30.23066581836549</v>
       </c>
       <c r="F31">
-        <v>0.1529197887788922</v>
+        <v>0.1516374760393585</v>
       </c>
       <c r="G31">
-        <v>0.8390764795331841</v>
+        <v>-2.66852928296312</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.7469126125113101</v>
       </c>
       <c r="E32">
-        <v>-27.79886848353549</v>
+        <v>-29.90147972156291</v>
       </c>
       <c r="F32">
-        <v>0.2819794301350552</v>
+        <v>-0.2730358417820444</v>
       </c>
       <c r="G32">
-        <v>3.078955175403137</v>
+        <v>-2.562479267158107</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.3007453149998839</v>
       </c>
       <c r="E33">
-        <v>-29.12287654305411</v>
+        <v>-30.07234810282033</v>
       </c>
       <c r="F33">
-        <v>0.62983823869486</v>
+        <v>-0.1538064363949032</v>
       </c>
       <c r="G33">
-        <v>1.975080249697474</v>
+        <v>-2.486704190309729</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.1954912170954072</v>
       </c>
       <c r="E34">
-        <v>-27.04313862723944</v>
+        <v>-29.16743672728958</v>
       </c>
       <c r="F34">
-        <v>0.5031742358675931</v>
+        <v>-0.1452228933670947</v>
       </c>
       <c r="G34">
-        <v>1.668195988752574</v>
+        <v>-2.205066149647311</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.7267051467435275</v>
       </c>
       <c r="E35">
-        <v>-28.29310613673264</v>
+        <v>-29.44672130476464</v>
       </c>
       <c r="F35">
-        <v>-0.2296807486543239</v>
+        <v>0.1694945921415075</v>
       </c>
       <c r="G35">
-        <v>1.04454879897359</v>
+        <v>-2.809916061854314</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.276198100988042</v>
       </c>
       <c r="E36">
-        <v>-27.15317148867781</v>
+        <v>-28.88613245040711</v>
       </c>
       <c r="F36">
-        <v>0.5079514306795379</v>
+        <v>-0.1006583838312869</v>
       </c>
       <c r="G36">
-        <v>0.5809896598371416</v>
+        <v>-3.300730922415582</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.832842549390591</v>
       </c>
       <c r="E37">
-        <v>-27.09071477516402</v>
+        <v>-28.3886071250804</v>
       </c>
       <c r="F37">
-        <v>-0.1161372571199984</v>
+        <v>-0.1075031836806192</v>
       </c>
       <c r="G37">
-        <v>0.2223979881143651</v>
+        <v>-2.904236814813689</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.389879609523995</v>
       </c>
       <c r="E38">
-        <v>-28.79761436897918</v>
+        <v>-27.88879492037981</v>
       </c>
       <c r="F38">
-        <v>-0.1892787853175836</v>
+        <v>0.006745248513488622</v>
       </c>
       <c r="G38">
-        <v>1.078147525651653</v>
+        <v>-3.722471250299956</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.93836181439281</v>
       </c>
       <c r="E39">
-        <v>-27.43404103205555</v>
+        <v>-26.94958035424096</v>
       </c>
       <c r="F39">
-        <v>0.01127476147199632</v>
+        <v>0.07147139226603359</v>
       </c>
       <c r="G39">
-        <v>0.9049199197637487</v>
+        <v>-3.524083498313591</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.465495541313926</v>
       </c>
       <c r="E40">
-        <v>-27.0876308843648</v>
+        <v>-26.4043792545615</v>
       </c>
       <c r="F40">
-        <v>1.005135060737593</v>
+        <v>-0.3016277710570721</v>
       </c>
       <c r="G40">
-        <v>2.475892957787341</v>
+        <v>-2.996077969164151</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.967717484706239</v>
       </c>
       <c r="E41">
-        <v>-24.56792907633491</v>
+        <v>-26.32788427162393</v>
       </c>
       <c r="F41">
-        <v>0.3458051385207571</v>
+        <v>-0.1605037868465372</v>
       </c>
       <c r="G41">
-        <v>0.1437692210111352</v>
+        <v>-3.171242244192529</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.439968126874802</v>
       </c>
       <c r="E42">
-        <v>-24.2334107013883</v>
+        <v>-26.00501313182505</v>
       </c>
       <c r="F42">
-        <v>0.5280111757057308</v>
+        <v>-0.4228659673960022</v>
       </c>
       <c r="G42">
-        <v>0.8687621413838288</v>
+        <v>-3.560453151608024</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.87443987589868</v>
       </c>
       <c r="E43">
-        <v>-24.09996562933027</v>
+        <v>-25.59201630232551</v>
       </c>
       <c r="F43">
-        <v>0.3013963620566756</v>
+        <v>-0.1264446327130327</v>
       </c>
       <c r="G43">
-        <v>1.647793096594046</v>
+        <v>-3.237244590608978</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.266595193691762</v>
       </c>
       <c r="E44">
-        <v>-24.32393942527564</v>
+        <v>-24.5451372666543</v>
       </c>
       <c r="F44">
-        <v>0.07672075649757405</v>
+        <v>-0.1277170050437327</v>
       </c>
       <c r="G44">
-        <v>1.027628600722374</v>
+        <v>-2.180720397751511</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.619070656966112</v>
       </c>
       <c r="E45">
-        <v>-23.3821934421665</v>
+        <v>-23.62054514308623</v>
       </c>
       <c r="F45">
-        <v>0.9511139089314258</v>
+        <v>-0.04094303449827612</v>
       </c>
       <c r="G45">
-        <v>0.4289660981282694</v>
+        <v>-3.324580092480491</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.93550786820157</v>
       </c>
       <c r="E46">
-        <v>-21.64520213857038</v>
+        <v>-24.32940076492889</v>
       </c>
       <c r="F46">
-        <v>1.153472468291706</v>
+        <v>-0.02073666844178778</v>
       </c>
       <c r="G46">
-        <v>-0.06599025490262649</v>
+        <v>-2.515174881947461</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.215748072815544</v>
       </c>
       <c r="E47">
-        <v>-21.61176841497175</v>
+        <v>-23.14957026086648</v>
       </c>
       <c r="F47">
-        <v>0.4578194638295146</v>
+        <v>-0.2794391218056846</v>
       </c>
       <c r="G47">
-        <v>1.210042970481756</v>
+        <v>-2.965048225824562</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.4711912187956</v>
       </c>
       <c r="E48">
-        <v>-20.4245927260689</v>
+        <v>-22.99874943404102</v>
       </c>
       <c r="F48">
-        <v>0.5181080434052626</v>
+        <v>-0.1412914616734082</v>
       </c>
       <c r="G48">
-        <v>0.5345758113765595</v>
+        <v>-2.582130665479221</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.713111098674824</v>
       </c>
       <c r="E49">
-        <v>-19.02423459478096</v>
+        <v>-21.37276914226893</v>
       </c>
       <c r="F49">
-        <v>-0.04095546000931811</v>
+        <v>0.1244918762496187</v>
       </c>
       <c r="G49">
-        <v>0.2715529682814637</v>
+        <v>-3.088816281355755</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.954154654961054</v>
       </c>
       <c r="E50">
-        <v>-18.25545820486881</v>
+        <v>-21.80058766719557</v>
       </c>
       <c r="F50">
-        <v>1.11416974849848</v>
+        <v>-0.470107760377658</v>
       </c>
       <c r="G50">
-        <v>1.023950584628244</v>
+        <v>-2.393555370471256</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.200736738481448</v>
       </c>
       <c r="E51">
-        <v>-18.46428425525852</v>
+        <v>-20.69896390924563</v>
       </c>
       <c r="F51">
-        <v>0.6846819593320068</v>
+        <v>-0.3478249927437977</v>
       </c>
       <c r="G51">
-        <v>-0.08047389163693792</v>
+        <v>-3.151686851692054</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.467523736271874</v>
       </c>
       <c r="E52">
-        <v>-17.50482741030538</v>
+        <v>-20.46543503314408</v>
       </c>
       <c r="F52">
-        <v>0.5826130130612601</v>
+        <v>-0.06993175175924482</v>
       </c>
       <c r="G52">
-        <v>0.5699655431913685</v>
+        <v>-2.092272552578803</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.764939994408603</v>
       </c>
       <c r="E53">
-        <v>-19.86946521136462</v>
+        <v>-18.72360279083375</v>
       </c>
       <c r="F53">
-        <v>0.8545212995605866</v>
+        <v>-0.2245920876989265</v>
       </c>
       <c r="G53">
-        <v>0.8872151222197264</v>
+        <v>-2.906524401781326</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.095724116728656</v>
       </c>
       <c r="E54">
-        <v>-17.86322442869444</v>
+        <v>-18.99613541356337</v>
       </c>
       <c r="F54">
-        <v>1.160210408746077</v>
+        <v>-0.2443411949490695</v>
       </c>
       <c r="G54">
-        <v>-1.200348683933899</v>
+        <v>-2.802510371482965</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.462406666275054</v>
       </c>
       <c r="E55">
-        <v>-15.92026001333343</v>
+        <v>-17.41619611702726</v>
       </c>
       <c r="F55">
-        <v>0.5460488759016899</v>
+        <v>-0.1254240840727837</v>
       </c>
       <c r="G55">
-        <v>-0.6825098401355604</v>
+        <v>-3.159423596617331</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.8662599048365</v>
       </c>
       <c r="E56">
-        <v>-16.52179080119431</v>
+        <v>-18.0791647117502</v>
       </c>
       <c r="F56">
-        <v>1.052612110061644</v>
+        <v>0.176698075076252</v>
       </c>
       <c r="G56">
-        <v>0.1189500611032191</v>
+        <v>-2.51468161066211</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.307547846967267</v>
       </c>
       <c r="E57">
-        <v>-13.99221239135369</v>
+        <v>-16.82261732952385</v>
       </c>
       <c r="F57">
-        <v>0.8372051073724658</v>
+        <v>-0.0894025275620472</v>
       </c>
       <c r="G57">
-        <v>0.05057405353511201</v>
+        <v>-2.615461237968603</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.770895911560661</v>
       </c>
       <c r="E58">
-        <v>-15.50823227727154</v>
+        <v>-16.89866852200867</v>
       </c>
       <c r="F58">
-        <v>0.6695534854546794</v>
+        <v>0.007299426305961492</v>
       </c>
       <c r="G58">
-        <v>0.009678884488495037</v>
+        <v>-3.384712841655813</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.25292215885979</v>
       </c>
       <c r="E59">
-        <v>-13.38897436879193</v>
+        <v>-16.72536835020913</v>
       </c>
       <c r="F59">
-        <v>0.7866067696746664</v>
+        <v>0.1479305319118308</v>
       </c>
       <c r="G59">
-        <v>-0.8182157228813649</v>
+        <v>-3.116575205702544</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.74193855271477</v>
       </c>
       <c r="E60">
-        <v>-11.41607674024022</v>
+        <v>-15.73413067467017</v>
       </c>
       <c r="F60">
-        <v>1.473046671882922</v>
+        <v>-0.05483889768023782</v>
       </c>
       <c r="G60">
-        <v>-0.1637341119496083</v>
+        <v>-3.51795898906594</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.2261609297157</v>
       </c>
       <c r="E61">
-        <v>-12.56298070979285</v>
+        <v>-14.4947507374069</v>
       </c>
       <c r="F61">
-        <v>0.4453591613566045</v>
+        <v>-0.09781791200708738</v>
       </c>
       <c r="G61">
-        <v>-0.00481468388243422</v>
+        <v>-3.32299765171272</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.68771170347796</v>
       </c>
       <c r="E62">
-        <v>-12.87204906081636</v>
+        <v>-14.73241863875146</v>
       </c>
       <c r="F62">
-        <v>0.3977180952867993</v>
+        <v>0.06815709428743277</v>
       </c>
       <c r="G62">
-        <v>-0.6965895903140807</v>
+        <v>-4.335296266711063</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.11539918640376</v>
       </c>
       <c r="E63">
-        <v>-11.08551625157632</v>
+        <v>-15.62736284299132</v>
       </c>
       <c r="F63">
-        <v>0.7302595622014384</v>
+        <v>0.1332253537773339</v>
       </c>
       <c r="G63">
-        <v>-2.043097709138468</v>
+        <v>-4.411879116671024</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.49911912500893</v>
       </c>
       <c r="E64">
-        <v>-12.43361126434173</v>
+        <v>-14.42693683914203</v>
       </c>
       <c r="F64">
-        <v>0.2707426263160799</v>
+        <v>0.1199184598187627</v>
       </c>
       <c r="G64">
-        <v>-0.7494556920307023</v>
+        <v>-3.990281142244838</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.8211277751587</v>
       </c>
       <c r="E65">
-        <v>-11.24757675088881</v>
+        <v>-14.14655184248312</v>
       </c>
       <c r="F65">
-        <v>0.485276529762707</v>
+        <v>-0.09023089496484669</v>
       </c>
       <c r="G65">
-        <v>-0.8152594057147957</v>
+        <v>-3.39980892931489</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-13.07221282312647</v>
       </c>
       <c r="E66">
-        <v>-11.51636432561409</v>
+        <v>-13.78601738436244</v>
       </c>
       <c r="F66">
-        <v>0.0992722306713878</v>
+        <v>-0.340295961419753</v>
       </c>
       <c r="G66">
-        <v>-0.8462394908712955</v>
+        <v>-4.36588239694839</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-13.23970967817717</v>
       </c>
       <c r="E67">
-        <v>-10.36646703474239</v>
+        <v>-14.25479595668846</v>
       </c>
       <c r="F67">
-        <v>0.7070719018622746</v>
+        <v>-0.3180493264501695</v>
       </c>
       <c r="G67">
-        <v>-1.56486954271751</v>
+        <v>-4.022631793254596</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-13.31996517035895</v>
       </c>
       <c r="E68">
-        <v>-10.41604023970435</v>
+        <v>-13.55647809386165</v>
       </c>
       <c r="F68">
-        <v>0.962611648482283</v>
+        <v>-0.424275848715567</v>
       </c>
       <c r="G68">
-        <v>-1.732078576815019</v>
+        <v>-4.066711707109992</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-13.30106461049255</v>
       </c>
       <c r="E69">
-        <v>-12.06010725666308</v>
+        <v>-14.81151749424344</v>
       </c>
       <c r="F69">
-        <v>0.9992221742164099</v>
+        <v>-0.548443152190796</v>
       </c>
       <c r="G69">
-        <v>-0.9425134656988409</v>
+        <v>-4.32967827093092</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.18046631962394</v>
       </c>
       <c r="E70">
-        <v>-11.63583452688445</v>
+        <v>-12.82956291767639</v>
       </c>
       <c r="F70">
-        <v>0.290400613151915</v>
+        <v>-0.6686185531519343</v>
       </c>
       <c r="G70">
-        <v>-0.3746853842575076</v>
+        <v>-4.377959267075651</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.95767712737581</v>
       </c>
       <c r="E71">
-        <v>-9.305160280882737</v>
+        <v>-13.66039298691566</v>
       </c>
       <c r="F71">
-        <v>0.1204038831168032</v>
+        <v>-0.4912377560882678</v>
       </c>
       <c r="G71">
-        <v>-1.972977044071165</v>
+        <v>-4.462881381249035</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.63807931011751</v>
       </c>
       <c r="E72">
-        <v>-10.16305251079184</v>
+        <v>-13.11403259789023</v>
       </c>
       <c r="F72">
-        <v>0.1033867315610929</v>
+        <v>-0.4313790991945727</v>
       </c>
       <c r="G72">
-        <v>-0.6330701530520845</v>
+        <v>-4.250440363448464</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.22668681528576</v>
       </c>
       <c r="E73">
-        <v>-10.14644206813171</v>
+        <v>-13.64847857180148</v>
       </c>
       <c r="F73">
-        <v>0.3608574025970269</v>
+        <v>-0.8709025594459624</v>
       </c>
       <c r="G73">
-        <v>-1.484300795928267</v>
+        <v>-4.58918531466331</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.72930772161061</v>
       </c>
       <c r="E74">
-        <v>-11.45694621815944</v>
+        <v>-13.14848522814058</v>
       </c>
       <c r="F74">
-        <v>0.02474981401333588</v>
+        <v>-0.9945189985983298</v>
       </c>
       <c r="G74">
-        <v>-1.772341431663635</v>
+        <v>-3.258163927871633</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.16407524905603</v>
       </c>
       <c r="E75">
-        <v>-12.4925765243956</v>
+        <v>-13.15451262704479</v>
       </c>
       <c r="F75">
-        <v>-0.4030994644304004</v>
+        <v>-0.7695998530228052</v>
       </c>
       <c r="G75">
-        <v>-0.942344627876338</v>
+        <v>-3.330035871529211</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.54350756849092</v>
       </c>
       <c r="E76">
-        <v>-9.207254672836903</v>
+        <v>-13.16099287334977</v>
       </c>
       <c r="F76">
-        <v>0.1921371867296292</v>
+        <v>-1.040209259434542</v>
       </c>
       <c r="G76">
-        <v>-0.9068158531488797</v>
+        <v>-3.501866427199542</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.883541718851113</v>
       </c>
       <c r="E77">
-        <v>-11.21276184271784</v>
+        <v>-13.38927324807643</v>
       </c>
       <c r="F77">
-        <v>-0.3817772874823411</v>
+        <v>-1.152429848226597</v>
       </c>
       <c r="G77">
-        <v>0.3312619676277589</v>
+        <v>-3.655230759851819</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.194969696069395</v>
       </c>
       <c r="E78">
-        <v>-10.09515709999484</v>
+        <v>-14.28555788062257</v>
       </c>
       <c r="F78">
-        <v>-0.5182284511736841</v>
+        <v>-1.366976177184266</v>
       </c>
       <c r="G78">
-        <v>-1.312218638796951</v>
+        <v>-2.672962103440204</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.501519263854238</v>
       </c>
       <c r="E79">
-        <v>-12.17248586763743</v>
+        <v>-13.93844581946063</v>
       </c>
       <c r="F79">
-        <v>-0.4689811807098507</v>
+        <v>-1.294459238008392</v>
       </c>
       <c r="G79">
-        <v>0.6957066838639667</v>
+        <v>-2.640396266970394</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.81371447218123</v>
       </c>
       <c r="E80">
-        <v>-12.75335322860131</v>
+        <v>-14.74771582394937</v>
       </c>
       <c r="F80">
-        <v>-0.5721087805213751</v>
+        <v>-1.207143515181504</v>
       </c>
       <c r="G80">
-        <v>0.6699837450238296</v>
+        <v>-2.495794948360567</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.138239123166238</v>
       </c>
       <c r="E81">
-        <v>-14.09632200879004</v>
+        <v>-16.00362469134064</v>
       </c>
       <c r="F81">
-        <v>-0.4484517513662705</v>
+        <v>-1.31484618815869</v>
       </c>
       <c r="G81">
-        <v>1.217690330677473</v>
+        <v>-2.674057894013703</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.486018425695368</v>
       </c>
       <c r="E82">
-        <v>-12.66421474623432</v>
+        <v>-16.60068134688193</v>
       </c>
       <c r="F82">
-        <v>-0.7343553051358946</v>
+        <v>-1.410948404027072</v>
       </c>
       <c r="G82">
-        <v>0.8204943874212549</v>
+        <v>-1.916260777892371</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.865543942411316</v>
       </c>
       <c r="E83">
-        <v>-13.66156133320964</v>
+        <v>-16.68660461270347</v>
       </c>
       <c r="F83">
-        <v>-1.482621236819494</v>
+        <v>-1.556058492179878</v>
       </c>
       <c r="G83">
-        <v>0.8359678772718084</v>
+        <v>-1.644402088752961</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.278928116786446</v>
       </c>
       <c r="E84">
-        <v>-13.19430432815019</v>
+        <v>-17.21110605769388</v>
       </c>
       <c r="F84">
-        <v>-0.7547240312033318</v>
+        <v>-2.092566379583631</v>
       </c>
       <c r="G84">
-        <v>1.463978366071553</v>
+        <v>-2.099698106223388</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.72284071438324</v>
       </c>
       <c r="E85">
-        <v>-15.56041388326192</v>
+        <v>-18.08177764125262</v>
       </c>
       <c r="F85">
-        <v>-1.042015928740048</v>
+        <v>-1.90441929138578</v>
       </c>
       <c r="G85">
-        <v>1.77750358136823</v>
+        <v>-2.306656860610926</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.206282014698384</v>
       </c>
       <c r="E86">
-        <v>-16.86344605117701</v>
+        <v>-20.33583010704455</v>
       </c>
       <c r="F86">
-        <v>-1.4051274662876</v>
+        <v>-1.916619486494211</v>
       </c>
       <c r="G86">
-        <v>1.190633241985009</v>
+        <v>-1.863818426004777</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.728942328119372</v>
       </c>
       <c r="E87">
-        <v>-16.70588232655412</v>
+        <v>-20.34665315992289</v>
       </c>
       <c r="F87">
-        <v>-2.111112697364909</v>
+        <v>-1.980484956515247</v>
       </c>
       <c r="G87">
-        <v>1.331212247764621</v>
+        <v>-0.9822698070799486</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.290860025480228</v>
       </c>
       <c r="E88">
-        <v>-18.94859549343085</v>
+        <v>-21.20837195036847</v>
       </c>
       <c r="F88">
-        <v>-2.165005452223642</v>
+        <v>-1.989538183860443</v>
       </c>
       <c r="G88">
-        <v>1.769571514256137</v>
+        <v>-2.155348376738536</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.895158468860747</v>
       </c>
       <c r="E89">
-        <v>-20.98920739381925</v>
+        <v>-22.74634134980149</v>
       </c>
       <c r="F89">
-        <v>-1.93575808696849</v>
+        <v>-2.643670928992115</v>
       </c>
       <c r="G89">
-        <v>2.111607147737018</v>
+        <v>-1.583564193377774</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.55111581302339</v>
       </c>
       <c r="E90">
-        <v>-20.97473891936474</v>
+        <v>-23.45084510812278</v>
       </c>
       <c r="F90">
-        <v>-2.539116052145566</v>
+        <v>-3.074986925016566</v>
       </c>
       <c r="G90">
-        <v>1.25131554171985</v>
+        <v>-1.811630986123706</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.264801116390508</v>
       </c>
       <c r="E91">
-        <v>-25.17716732695684</v>
+        <v>-24.77842160515944</v>
       </c>
       <c r="F91">
-        <v>-2.157144245571075</v>
+        <v>-2.976961240038884</v>
       </c>
       <c r="G91">
-        <v>1.132221976490108</v>
+        <v>-2.112337769092326</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.044529782930405</v>
       </c>
       <c r="E92">
-        <v>-25.89368059834647</v>
+        <v>-26.97814596828135</v>
       </c>
       <c r="F92">
-        <v>-2.651565270340793</v>
+        <v>-3.030738851828628</v>
       </c>
       <c r="G92">
-        <v>0.9914542696147582</v>
+        <v>-2.020215218371026</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.905985040479309</v>
       </c>
       <c r="E93">
-        <v>-29.003555781426</v>
+        <v>-28.398411271307</v>
       </c>
       <c r="F93">
-        <v>-2.006701956446448</v>
+        <v>-2.752079370996486</v>
       </c>
       <c r="G93">
-        <v>1.463905534069689</v>
+        <v>-2.358182191384143</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.858324395525341</v>
       </c>
       <c r="E94">
-        <v>-31.08197138283044</v>
+        <v>-30.27372254923042</v>
       </c>
       <c r="F94">
-        <v>-2.942863152637448</v>
+        <v>-3.338139368068302</v>
       </c>
       <c r="G94">
-        <v>1.4555861331295</v>
+        <v>-1.74038804611859</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.911696444913763</v>
       </c>
       <c r="E95">
-        <v>-30.45363202884415</v>
+        <v>-32.76157786380136</v>
       </c>
       <c r="F95">
-        <v>-2.011012780410617</v>
+        <v>-3.401400958252698</v>
       </c>
       <c r="G95">
-        <v>1.003733083019915</v>
+        <v>-2.198233183654255</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.076666722646522</v>
       </c>
       <c r="E96">
-        <v>-33.90445828419818</v>
+        <v>-33.49967384231155</v>
       </c>
       <c r="F96">
-        <v>-3.5263295313711</v>
+        <v>-3.484793533059927</v>
       </c>
       <c r="G96">
-        <v>1.633117448218457</v>
+        <v>-2.40879712213406</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.350717836047135</v>
       </c>
       <c r="E97">
-        <v>-34.56137910188388</v>
+        <v>-35.66239151584278</v>
       </c>
       <c r="F97">
-        <v>-3.502976197551376</v>
+        <v>-3.820725507754224</v>
       </c>
       <c r="G97">
-        <v>0.6771775604806659</v>
+        <v>-2.70677601557832</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.742184220605242</v>
       </c>
       <c r="E98">
-        <v>-36.70220613206202</v>
+        <v>-38.48150923254882</v>
       </c>
       <c r="F98">
-        <v>-3.128060424513931</v>
+        <v>-4.038279638751458</v>
       </c>
       <c r="G98">
-        <v>0.6702254148481964</v>
+        <v>-3.06821806701041</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.22199525750233</v>
       </c>
       <c r="E99">
-        <v>-38.64752535390701</v>
+        <v>-41.37829480696041</v>
       </c>
       <c r="F99">
-        <v>-3.946513926236732</v>
+        <v>-3.984821776779195</v>
       </c>
       <c r="G99">
-        <v>0.04957426878225211</v>
+        <v>-2.900697841632209</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.810465764224286</v>
       </c>
       <c r="E100">
-        <v>-41.13370966156914</v>
+        <v>-42.44397606671147</v>
       </c>
       <c r="F100">
-        <v>-3.863579438603251</v>
+        <v>-4.256708525726049</v>
       </c>
       <c r="G100">
-        <v>-0.8451403897522575</v>
+        <v>-3.751895379052999</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.431426328491781</v>
       </c>
       <c r="E101">
-        <v>-43.33716095879935</v>
+        <v>-44.73036636539217</v>
       </c>
       <c r="F101">
-        <v>-3.974539252208245</v>
+        <v>-4.518586111344876</v>
       </c>
       <c r="G101">
-        <v>-0.7540507292392107</v>
+        <v>-3.53694496773366</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.151886012497165</v>
       </c>
       <c r="E102">
-        <v>-46.35663195102675</v>
+        <v>-47.56402048366283</v>
       </c>
       <c r="F102">
-        <v>-4.133041556162111</v>
+        <v>-4.508054248185683</v>
       </c>
       <c r="G102">
-        <v>-1.622774294744902</v>
+        <v>-4.260411726612749</v>
       </c>
     </row>
   </sheetData>
